--- a/AAII_Financials/Quarterly/PBR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBR_QTR_FIN.xlsx
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32722700</v>
+      </c>
+      <c r="E8" s="3">
         <v>23709500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23124700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24000100</v>
       </c>
-      <c r="G8" s="3">
-        <v>21866200</v>
-      </c>
       <c r="H8" s="3">
+        <v>21863200</v>
+      </c>
+      <c r="I8" s="3">
         <v>21478000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19607100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23797500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22024800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20738000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>27668900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24995100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23609900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>27464800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>28501400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31423200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34263800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29125600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>27084900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24489000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21436800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16122300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14672000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13776800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9913900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13472700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>15103100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14453200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12849400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13259300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>14768100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16481000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>17473800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>17388100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>19616100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>18413700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>17176400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>16960000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>17486900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>17475500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13748800</v>
+      </c>
+      <c r="E9" s="3">
         <v>12284300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12505100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12532200</v>
       </c>
-      <c r="G9" s="3">
-        <v>11464100</v>
-      </c>
       <c r="H9" s="3">
+        <v>11461100</v>
+      </c>
+      <c r="I9" s="3">
         <v>10889500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10207400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11570600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11028500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8481000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12701600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11716400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11647100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12986500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15843900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16404500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16120200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14855700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16290100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13527400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11394000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8754100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8334500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8299000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7527700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8814400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9428600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9866300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8263300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9194100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>21383600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>22913600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>22719600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>11136100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>13154600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>12969000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>11697900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>11059200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>11827700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>11686100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>18973900</v>
+      </c>
+      <c r="E10" s="3">
         <v>11425200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10619600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11467900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10402100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10588500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9399700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12226900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10996300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12257000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14967300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13278700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11962800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14478300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12657500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15018800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18143600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14269900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10794800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10961600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10042800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7368200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6337500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>5477800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2386200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4658300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5674500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4586900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4586100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4065200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-6615400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-6432600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-5245800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6252000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6461500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5444700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>5478600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5900800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5659200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5789400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,130 +1219,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>288400</v>
+      </c>
+      <c r="E12" s="3">
         <v>252300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>230900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>237900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>201000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>205600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>207100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>199100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>181600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>183000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>218700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>181800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>176300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>158000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>788800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>286200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>255700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>306200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>335300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>299700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>344700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>343300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>477700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>378300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>139500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>158900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>456600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>160200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>171000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>219500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>196100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>192100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>274600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>218800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>387900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>281000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>295300</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>157000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>430200</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>583000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1451,235 +1467,241 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>997300</v>
+      </c>
+      <c r="E14" s="3">
         <v>149500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2160100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>540800</v>
       </c>
-      <c r="G14" s="3">
-        <v>-523100</v>
-      </c>
       <c r="H14" s="3">
+        <v>849400</v>
+      </c>
+      <c r="I14" s="3">
         <v>675500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1311700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>985800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>657800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>693000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2037800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>693600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>497100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-181500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1229400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>421300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2419500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>140000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-100900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-4152900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-614800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-61700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-6072800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>449900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-3069100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>11707700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1711800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1138200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>166400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>244600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1992700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>430600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>319700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>310600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>931700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>434100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>34900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>306100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>770000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>4455000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E15" s="3">
         <v>16300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>556500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>219800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>897000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>314200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>53000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>50000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>322500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>367200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>32600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>199000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>213400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>237300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>238100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>206900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>188500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>164200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>177000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>171800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>195900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>158200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>120700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>127300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>127700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>131900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>125900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>36000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>40500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>46900</v>
       </c>
-      <c r="AJ15" s="3" t="s">
+      <c r="AK15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AK15" s="3">
-        <v>0</v>
-      </c>
       <c r="AL15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>18102600</v>
+      </c>
+      <c r="E17" s="3">
         <v>16135000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16915600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15306200</v>
       </c>
-      <c r="G17" s="3">
-        <v>16844200</v>
-      </c>
       <c r="H17" s="3">
+        <v>15380500</v>
+      </c>
+      <c r="I17" s="3">
         <v>13858700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16728200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14255500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15145500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11333000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18276100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14538400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14508200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15793600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18111000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17637900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14936500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15677800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15295800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>11104800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10889000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9779200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1349700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10264500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6439000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>21584700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12492400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11770300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5901700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10634600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12771800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13412800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13543700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>13108600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>19854600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>16307300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>13175600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>13268100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>14717100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>19999000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>14620100</v>
+      </c>
+      <c r="E18" s="3">
         <v>7574500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6209200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8693800</v>
       </c>
-      <c r="G18" s="3">
-        <v>5022000</v>
-      </c>
       <c r="H18" s="3">
+        <v>6482700</v>
+      </c>
+      <c r="I18" s="3">
         <v>7619300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2878900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9542000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6879300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9405000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9392900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10456700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9101800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11671200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10390400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13785300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19327300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13447800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11789100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13384200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10547800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6343100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13322300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3512300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3474900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8111900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2610700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2683000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6947700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2624700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1996300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3068200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3930100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4279500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-238400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2106400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4000800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3691900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2769800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-2523500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-364200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2383900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3469700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-714300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1566000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1477800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2834000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6695000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-34200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6441200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1467000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>459200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1839600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-217600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>293300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>946500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-850100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2441300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1243900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2086000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4391900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2604700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4897300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2236900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3309100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3126800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2918800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-418300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1043700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-589500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-658300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-643100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-406000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>202000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-542000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-986300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-870400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1161400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-656200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-233200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-430200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>14988400</v>
+      </c>
+      <c r="E21" s="3">
         <v>9974600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3295900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9425300</v>
       </c>
-      <c r="G21" s="3">
-        <v>6588200</v>
-      </c>
       <c r="H21" s="3">
+        <v>7960700</v>
+      </c>
+      <c r="I21" s="3">
         <v>10673100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2919000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9890400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>491000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7988000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9256200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8984400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9326000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11410500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14474700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16102600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>20292300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18105900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12978500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12267500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16043000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4370000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17927500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3216400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3264900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-8217600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4952700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4450100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8960500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4563000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3284200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4623200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6642500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6319500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1453200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4026700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>5501100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5706600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>5322300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>200900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>578700</v>
+      </c>
+      <c r="E22" s="3">
         <v>610200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-2003600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>756200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>731000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>650700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-1295600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>714400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>651000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>725000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>-1098000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>801500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>609100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>645000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>678700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>623000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>716700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>630500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>724200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>739500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>962100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>855400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>916700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1153300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>988500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>861900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>798800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>996000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>929100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>917100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>633700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>742000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>889500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>1150100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>961700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1029600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>1103700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1267700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1239900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>1336700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>13671600</v>
+      </c>
+      <c r="E23" s="3">
         <v>9418900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2900000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8434500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6614300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9354700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3519200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8246000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-513900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6952000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8448800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7566100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8648800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11256400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10658200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12312200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16169300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14061200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8978900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8252800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12190400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>590500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14642500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-950100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-640400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11892600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1393600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>643200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5429100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1049200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>719500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1920200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3242700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2587400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2186400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>206400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1735700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1768100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1296700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-4290300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3539000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3138900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>58100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2271200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3192500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-776700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2245100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-60900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2147000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2026500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2207800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2647600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3691100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2839600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3769700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5249600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4852500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2575900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1964300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3856300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>351700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2812000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-625000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-92500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3015900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-183400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>738700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2056000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>345100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>474400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>842400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1041000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>923600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-809100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>39700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1660800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>575500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>612000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-240900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>10132600</v>
+      </c>
+      <c r="E26" s="3">
         <v>6280000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2841900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6163400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4913700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6162200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2742500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6000900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-453000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4805000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6422300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5358300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6001200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7565300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7818600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8542600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10919700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9208700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6403000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6288500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8334000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>238700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11830500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-325100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-547900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8876700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1577000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-95500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3373200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>704200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>245100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1077800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2201600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1663800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1377300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>166600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>74900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1192500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>684700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-4049400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6261200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2825500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6136700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4891400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6140900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2755700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5978700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-469200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4782000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6397600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5331300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5969300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7535500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7789700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8516700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10888800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9163100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6358800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6272000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8298000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>218300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11720500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-301100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-528400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8662300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1505900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-49100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3287100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>665100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>88800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1029700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2290600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1625500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1404200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>68200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>81000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1103700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>622700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-4082900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3187,12 +3247,12 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
@@ -3206,29 +3266,29 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>1753700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>53500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>89300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>286200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>199600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>61400</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
       <c r="AL29" s="3">
         <v>0</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>364200</v>
+      </c>
+      <c r="E32" s="3">
         <v>2383900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3469700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>714300</v>
       </c>
-      <c r="G32" s="3">
-        <v>1566000</v>
-      </c>
       <c r="H32" s="3">
+        <v>1477800</v>
+      </c>
+      <c r="I32" s="3">
         <v>2834000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6695000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>34200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6441200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1467000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-459200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1839600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>217600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-293300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-946500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>850100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2441300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1243900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2086000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4391900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2604700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4897300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2236900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3309100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3126800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2918800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>418300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1043700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>589500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>658300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>643100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>406000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-202000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>542000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>986300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>870400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1161400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>656200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>233200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>430200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6261200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2825500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6136700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4891400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6140900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2755700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5978700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-469200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4782000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6397600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5331300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5969300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7535500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7789700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8516700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10888800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9163100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6358800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6272000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8298000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>218300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11720500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-301100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-528400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8662300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1505900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1704500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3340600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>754300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>375000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1229300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2352000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1625500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1404200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>68200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>81000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1103700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>622700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-4082900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6261200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2825500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6136700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4891400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6140900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2755700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5978700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-469200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4782000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6397600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5331300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5969300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7535500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7789700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8516700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10888800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9163100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6358800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6272000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8298000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>218300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11720500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-301100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-528400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8662300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1505900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1704500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3340600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>754300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>375000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1229300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2352000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1625500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1404200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>68200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>81000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1103700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>622700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-4082900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4191,1106 +4276,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>6477800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6573900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6464800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8945700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7006500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4702200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3274700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8698900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7894800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11502100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12697700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12142700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10345300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10324300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7498900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4369600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17098000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16779600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11789500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11962000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9512300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12751100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11909500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13953100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>20763200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14349800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5488200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10294800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>11341700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6825800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>9607600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>10510300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>15304000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>15496900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>19098800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>19082600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>19989900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>15101600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>17144300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>17380500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>3899800</v>
+      </c>
+      <c r="E42" s="3">
         <v>2550600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2723300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2688100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2508800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2978600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4268000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5595900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4295700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4799500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2813100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1302500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2302700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2889100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2600700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2408900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2997700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1227000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>732700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>588100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>583400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>617200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>670100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>736700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>575000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>597300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>661200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1018000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>434900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>817800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>748900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>770500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>948100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>911900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1599000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1472600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>850400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>721700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>634100</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>630600</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>8367000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6327000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6646300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6029800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5235800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4701000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5538500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6818500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7214700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6556700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7296500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6300800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5681400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5845600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5924100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5503800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6637700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6790700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8689000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6758400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6207000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4113000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7449700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7159500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8590600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5179900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5439600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5305300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4344400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5171300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5378200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6494700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6629900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5596300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>6283400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>6261800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>5855200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>5509600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>5878500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>6366200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>9710300</v>
+      </c>
+      <c r="E44" s="3">
         <v>9307800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8201300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8682400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8245300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7461200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6718000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7445800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7348500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8144600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7663200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7911300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8138400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7995100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8232400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9759900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>9985300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9942400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8171700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7970800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6978000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7433100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5773200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5802500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5374800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5576300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6096800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5924300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6062500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6168200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6212200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>7191200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>8297900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>6856400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>7199400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>6627700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>6825100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>6492700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>6852500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>6853700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1457700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1570700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>919400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1679900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1937300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1933000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1701200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2178200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1942500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2087300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1901600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1839600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1907200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3990500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5049300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7395000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8332700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6285900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4576100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6220400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6061800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3892200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2050200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1885500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4027700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3495800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3019300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5144600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9925100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5457100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3672400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2825000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2506600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5095200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5791400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3459100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2996800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>5431500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>5687200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>4679300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>29912600</v>
+      </c>
+      <c r="E46" s="3">
         <v>26938900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25422300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28025900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24933700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21776100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21861600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>30737300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28696200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33090200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32372100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29497000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28375100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31044500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>29305300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>29437300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>45051400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>41025700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>33959000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>33499700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>29342500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>28806600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27852600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>29537200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>39331100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>29199100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>20705100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>27687000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>32108600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>24440100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25619300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>27791700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>33686400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>33956600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>39971900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>36903800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>36517500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>33257100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>36196600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>35910300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>653800</v>
+      </c>
+      <c r="E47" s="3">
         <v>592500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>551600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>845300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>830100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1566900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1242700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1617400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2332500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3102800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3758000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5302100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4833400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4292900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5223000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3662100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3934000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3937200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3890900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4001000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3693900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6162900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6049500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5885700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6188700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5746900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6047600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6388200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5948100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6011700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5740200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5814000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7374100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>6774200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7661900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7536000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7805700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>6431000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>6220100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>6254300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>185543700</v>
+      </c>
+      <c r="E48" s="3">
         <v>180931300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>167869300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>171209100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>163876600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>152659500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>136448000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>141154600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>136129900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>149632700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>153076700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>145262600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>146555600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>134022100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>122069400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>123986300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>133764900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>141278300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>141168100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>141759000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>121957700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>118748300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>126311400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>115086500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>115173200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>105293600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>118568000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>125442600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>119960000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>132717600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>108793500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>113003000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>141392600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>136830300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>149817400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>146337300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>147480500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>141215800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>141871000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>142245600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>2730100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2683300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2520900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2512700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2435800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2285500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2257300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2559000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2691700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2954600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3034800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2924100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3384900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3060900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2800400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2849400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3415600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3488700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3406900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3343400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>15033200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14515600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15201600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15115700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15282600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>14017700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>14496900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1858400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1753000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2031100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1939200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2008500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1804200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1822900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1984400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2624800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2704800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2628900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2645300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2700600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>26286500</v>
+      </c>
+      <c r="E52" s="3">
         <v>25472300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23882900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18418800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17292600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15801700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17871600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19883600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18574500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21400300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21527900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19810600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19596000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18161200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16145900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15138700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15206900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15625000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13955600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>13699200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12265100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18535400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17822800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>22421300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>21753600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>19200700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11216600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12034900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11146700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12402000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11416200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11758700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>14300500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>13072200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>13748100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>12694100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>12660300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>11965600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>12757800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>12148500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>246876700</v>
+      </c>
+      <c r="E54" s="3">
         <v>238860200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>222111300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>227424900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>215623600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>200177200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>181861800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>197944800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>190699600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>212798700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>216575200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>205341500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>205417000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>193261000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>175543900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>175073800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>201372800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>205354900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>196380400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>196302400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>182292400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>186768800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>193237900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>188046500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>197729400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>173458100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>171034200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>173411100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>170916500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>177602700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>153508400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>160375900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>198557900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>192456200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>213183800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>206096200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>207168900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>195498500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>199690800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>199259300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>6611900</v>
+      </c>
+      <c r="E57" s="3">
         <v>7492400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7434300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6805500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6308500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5453000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6088900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5301700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4818800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5144300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4802300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4682100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5427100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5064300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5123600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5203600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5803000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5763600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6175700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5941700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5165500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5436300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6975700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4760200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4172000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5402400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4169800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4568900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3865800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4287500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4373700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5080600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4850000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4209700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4891000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4858100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4358700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3702600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4659200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>4300200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>11675800</v>
+      </c>
+      <c r="E58" s="3">
         <v>12737300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12210100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12049400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11763700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11621000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11121100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11712000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12069100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12321400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11495800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11040800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10332000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9772500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8564100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8633500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9805100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8907500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>10219400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9977200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8172500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9232700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10051900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>13316700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12910400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10574500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7598400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10290800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7858400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6752200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2550400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3004000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3585200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3613500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>5959300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>4802500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>5517000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>7230800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>6593500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>7752500</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>8173300</v>
+      </c>
+      <c r="E59" s="3">
         <v>7589600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9104000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8551600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8639100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7172100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8998900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8574200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7761200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6686500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10735300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8958000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10329600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5244400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15739700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11254700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18695200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12106500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10835800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12008100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9109300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8617900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9643700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9329800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10998800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8094300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9684200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10212200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12772800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10206800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10392900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9321600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11332000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10418500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10310100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8605900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>8062600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>8535200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>8883200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>8495700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>35008500</v>
+      </c>
+      <c r="E60" s="3">
         <v>36261400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36014500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34219000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32884300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30318000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31497400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32860500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32057800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30680100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33783600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30950700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31441000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25367800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29427400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25091700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>34303300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26777500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27230800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27926900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>22447300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23286900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>26671400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27406700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>28081200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>24071100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21452400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>25071900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>24496900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>21246600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>17316900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>17406100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19767200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>18241600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>21160300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>18266600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>17938400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>19468600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>20135900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>20548500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>59072500</v>
+      </c>
+      <c r="E61" s="3">
         <v>58512600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57511300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58518200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56404900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>52966800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>49262600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47451500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47638500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>49278600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50961600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50121500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47609100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>43753900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>41886600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>45575700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46440100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>48138000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>55947400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>55301400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53512000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>66410800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>66769700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>74125700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>84392900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>72243800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>57261100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>59935600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>60696400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>70547100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>55764300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>62274800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>78992800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>76011900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>86717700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>86139300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>89887300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>81813600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>87802700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>89572800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>32586300</v>
+      </c>
+      <c r="E62" s="3">
         <v>32558500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31071900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>32888300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32515200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31106500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29525000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23666900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23430400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25955100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26605500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24905400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26227500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24914000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38739000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>35286800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37885600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>40566500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>34569100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37410300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>36163500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>37156400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>38904800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37748800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>37393700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>35204300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>37070200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>30300200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>30934500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>31722700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>29843100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>25893700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>32673000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>33341800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>36183400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>33872900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>32391000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>29587500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>29051700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>24137200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>153869100</v>
+      </c>
+      <c r="E66" s="3">
         <v>153294600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146296700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>147685900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>141885900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>130829900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>122440600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>125394100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>122964200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>131067700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>137779600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>127751900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>128207500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>113591800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>110374900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>106251000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>119091400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>116071600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>118201900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>121970300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>113350000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>128135700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>132882100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>139792400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>150443400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>132072000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>116447800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>115964400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>117154600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>124708700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>104051400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>106649600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>132672800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>128947400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>145503300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>138985100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>140860000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>131538500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>137613700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>134873900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>43719300</v>
+      </c>
+      <c r="E72" s="3">
         <v>36619300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28736000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29138900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24023300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21773600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15391200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27492700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23548000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>36461600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>32803200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29319000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28001900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>32925400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23664000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25229700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36147100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>43573400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33776100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33000600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31833900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23837500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>25433400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14507200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14810900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14059000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>23508200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>23613900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21144600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19060300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17451400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18721900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22235300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>20035100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>20464500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>21503600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>21437500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>20661300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>19557400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>18688600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>92833200</v>
+      </c>
+      <c r="E76" s="3">
         <v>85338800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>75487700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>79358700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>73267900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>69040000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59177400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>72293900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>67274100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>81275200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>78404300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>77292600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>76878100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>79408300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>65169000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>68822700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>82281400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>89283300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>78178500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74332100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>68942300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>58633100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60355800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>48254000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>47286000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>41386100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>54586400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>57446800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53761800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>52894000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>49456900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>53726200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>65885100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>63508800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>67680500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>67111100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>66308800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>63960000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>62077100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>64385400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>10123000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6261200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2825500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6136700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4891400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6140900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2755700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5978700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-469200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4782000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6397600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5331300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5969300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7535500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7789700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8516700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10888800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9163100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6358800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6272000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8298000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>218300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11720500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-301100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-528400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8662300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1505900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1704500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3340600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>754300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>375000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1229300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2352000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1625500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1404200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>68200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>81000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1103700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>622700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-4082900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>3800500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3280200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2794100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3004800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2915900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3285600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3674800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3370200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3309800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2975400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3282300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3148900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3231200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3473800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3137900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3167300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3406300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3414300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3275500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3275200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2890500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2924200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2368400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3013200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2916800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2813100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2760300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2810900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2579600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2620600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1949200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1979800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>2560100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>2582000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>2677900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>2790700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>2661700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>2670800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2785700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>3154600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>11931200</v>
+      </c>
+      <c r="E89" s="3">
         <v>8429600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9970200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10067700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7785900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8605200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7706800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11518400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8496600</v>
       </c>
-      <c r="L89" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11882600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11319000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9903400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10617000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12145300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11678100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14391000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10862200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10373000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11097100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10952500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7496700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7378300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8979900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5709000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6246600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5669000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6157100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3629900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3321400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4657700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4056800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5976900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5188300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>5016600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>6158800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5038600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5761700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>5849500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>6627500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-4447200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4549600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6466600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4996600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4252300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4063300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4189200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4524500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2748800</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="M91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3667100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3111700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2984200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2486800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18710000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10225000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8383000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12338000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9406000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7857000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1527700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1459100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1161100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1600100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1489200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2399100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1323800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1420800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1111600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1763300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2558200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2319300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2316300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3461400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2418200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2732200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-2486800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>5987900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-5057900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-5578100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3606100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6422800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4866800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2673100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1785100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3099300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4828700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1884300</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3292700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2758700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-830200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1133200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2210300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-706300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3352400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1024700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>627300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>4144600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1004400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1389500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-359100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-594300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2318900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1189700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5898800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-478500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5494300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-840800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-991400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2435500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>68700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>149000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3155500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2973800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-781700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2049600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1710800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1957600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10194,107 +10426,108 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1472500</v>
+      </c>
+      <c r="E96" s="3">
         <v>2231100</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2060700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1754100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2893000</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2335600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>6746500</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>4477100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>4766200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>6345300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>4305900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-3796800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-20516900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12431500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-8270600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4208300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1990900</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-348900</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-790300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-435900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-222100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-698400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-210200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-110100</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-6532000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4783300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5916800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3301500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2843400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5484300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9300900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6003300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9759000</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8022600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6956600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9022500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7161300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6647000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-22358400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-17978700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3383600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11248900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-13738700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12688000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5766500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7679900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-15376900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>704300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2284900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4849300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-9075100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3806500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5652100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3870600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3450400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-8230600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-7119100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2529200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3224700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-686800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5299000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-4395700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-3001000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-210900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-166200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>309600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-36700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>650100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>322400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-367200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>550900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-547300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-238200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-41800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>933100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1731000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-39700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>978300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1691700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>58100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>570600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-944700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1011800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1439400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>182100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1010300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1705900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>433300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1322800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-113100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-67700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-328300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>349200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2054300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-117200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>684300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-867600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>813000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-455700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-20100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-141700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-251900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2190800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1782200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2058600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1169600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4383700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>649700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2496600</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>200100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2154500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-496700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2084300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3248300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11399300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>743000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4762200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-190500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2073600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3684600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1352500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2100100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6809100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5104800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9047800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4645800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2073700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5216700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3251900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-526100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1615900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-192900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1899000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>16200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-907300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>4383100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2042700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-236200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1766300</v>
       </c>
     </row>
